--- a/baekhyejin_skinlab/ccminam_30개_분석.xlsx
+++ b/baekhyejin_skinlab/ccminam_30개_분석.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ccminam 30개" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ccminam 릴스 19개" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="성과 요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ccminam 30개'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ccminam 릴스 19개'!$A$1:$K$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -570,100 +570,44 @@
       </c>
     </row>
     <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 21:31</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="A2" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20 20:10</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>릴스</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>2904</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>어플리케이터 변경안내</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>어플리케이터 변경안내
-기존 어플리케이터 구성
-슈터(주사기)+큰니들+작은니들
-변경된 구성
-전뮨가용 니들 2개
-구매전 참고하세요🙌🏻</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-20 20:10</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>릴스</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="n">
-        <v>2904</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>모공주사 구매하지마세요!</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 링크 · 오픈 · 할인</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>여러분 이제 하루 남았어요. 모공주사 최저가 할인 내일 자정 오픈돼요. 역대 최대 할인인 만큼 조기 품절 예상돼요. 무조건 오픈난 하세요. 미리 회원금 필수인 거 아시죠? 댓글 달아주시면 대기방 링크 바로 전송해드릴게요.</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>모공주사 구매하지마세요!
 22일 단 하루!
@@ -675,103 +619,51 @@
 #슈젝홈 #슈퍼젝션</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 19:59</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>좋은 인사이트는</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>좋은 인사이트는
-좋은 공간과 좋은 사람들과 만들어짐🙌🏻</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="6" t="n">
+    <row r="3" ht="90" customHeight="1">
+      <c r="A3" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>2026-07-19 23:16</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D5" s="8" t="n">
+      <c r="D3" s="8" t="n">
         <v>2851</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E3" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F3" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>정가대비 최대 55% 할인이에요!</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 할인 · 특가</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>모공주사 원데이 프로모션 이제 이틀 남았어요. 22일 단 하루 정가 39만원, 특가 17만원대에 구매 가능해요. 이건 무조건 조기 품절이에요. 가장 빠르게 링크 올려드리는 대기방 1차는 이미 마감, 2차 대기방 오픈되었어요. 댓글 달아주시면 2차 대기방 바로 안내해드릴게요.</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>정가대비 최대 55% 할인이에요!
 역대 최대할인인만큼 이건 무조건 조기품절🙌🏻
@@ -782,104 +674,51 @@
 #모공주사 #슈젝홈</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 00:17</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+    <row r="4" ht="90" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-18 00:03</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>릴스</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>5346</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>모공주사 사용 휴</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>궁금해하시는 Q&amp;A 모음</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>궁금해하시는 Q&amp;A 모음
-무물은 실시간 진행중이니
-언제든 환영합니다</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-18 00:03</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>릴스</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>5346</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>모공주사 사용 휴</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>여러분, 휴식코마시면서 저한테 말씀해주신 걸 알겠습니다. 이 후에 만족이 있으시거든요? 이틀 3일차까지 피부가 더 많이 퍼지는 것 같아서요. 그러면 너무 정성적이에요. 피부가 상처가 나고 회복되는 기간 동안은 더 안 좋아져요. 3일차부터 서서히 얼굴이 강이 나고, 더 좋아서 이렇게 부담을 하고, 그것도 얼굴이 너무 박대하지 않고, 너무 영성과적인 힘이 없는 자료들에게 표창하러 쌓여가면서 피아노치창을 가지고 있어요.</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>모공주사 사용 휴
 데미지를 입은 피부가 회복되며
@@ -891,51 +730,51 @@
 회차가 쌓일수록 더 좋아짐🙌🏻</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="n">
+    <row r="5" ht="90" customHeight="1">
+      <c r="A5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>2026-07-17 23:31</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D5" s="10" t="n">
         <v>11984</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">피부가 민감할때는 </t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>댓글 · 할인</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>저 진짜 얼굴에 시술도 셀프케어도 많이 했거든요 그러다 보니까 어느 순간 살짝만 작업받아도 붉어지고 인간해지고 피부는 점점 더 탄력을 잃고 늘어지더라고요 그래서 회복이 필요하다 판단한 후 딱 두 가지만 했어요 장작크림 발라주고 유광팩 1시간씩 일주일에 3번 씹혔더니 붉었던 피부가 맑아지고 탄탄해지기 시작하더라고요 피부가 붉고 고민이라면 무조건 써보세요</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>피부가 민감할때는 
 회복이 필요하다고 말하는 신호일 수 있어요. 
@@ -946,51 +785,51 @@
 이번달에만 15% 추가할인에 55,000원짜리 클렌징 세트도 증정되는데 구매 원하시는 분들은 댓글 물광팩 달아주세요.</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="6" t="n">
+    <row r="6" ht="90" customHeight="1">
+      <c r="A6" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>2026-07-17 21:41</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D6" s="8" t="n">
         <v>4489</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E6" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>항상 코칭,케어 시작전</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>한 직업을 10년 가까이 하다보니 결국 남는 건 화려한 말보다 사람에 대한 기준이더라고요. 저는 온라인 상담도, 샵 관리도 상담을 가장 중요하게 생각해요. 사람마다 얼굴형도, 피부결도, 생활습관도 모두 다 다르기 때문에 무조건 빠르게 바꾸려고 하는 것보단 왜 같은 문제가 분복되는지, 어떻게 해야 오래 유지되는지를 먼저 봐요. 좋은 피부는 좋은 제품 하나보다 좋은 기준에서 시작된다고 저는 믿습니다.</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>항상 코칭,케어 시작전
 하나하나 꼬치꼬치 물어가는 과정은
@@ -1006,102 +845,102 @@
 #에스테틱</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="n">
+    <row r="7" ht="90" customHeight="1">
+      <c r="A7" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>2026-07-16 23:52</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D7" s="10" t="n">
         <v>8036</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E7" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>모공주사는 사용법이 중요하니</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>무조건 흉터 있다고 해서 세게 하는 거 절대 좋지 않아요 오히려 흉터 있는 주변 조직들은 굳어 있는 시간들이 오래 됐다면 재생이 엄청 더딜 수 있어요 그래서 주기 조정이 필요할 수도 있고 너무 강한 데미지는 회복이 너무 오래 걸릴 수도 있어요 그래서 적절하게 회복하는 속도를 보면서 진행하시는 걸 추천드려요 사진 보내주시면 제가 주기랑 이런 부분 정해드릴게요</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>모공주사는 사용법이 중요하니
 무조건 가이드 안내받고 사용하세요🙌🏻
 #슈젝홈 #모공주사</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="6" t="n">
+    <row r="8" ht="90" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>2026-07-16 21:41</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D8" s="11" t="n">
         <v>17272</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E8" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>모공주사 n년차</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>할인</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>후, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤, 벤</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>모공주사 n년차
 커버사진과 비교하면 정말 많이 개선된 모공
@@ -1113,51 +952,51 @@
 🔻모공🔻</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="n">
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2026-07-16 18:10</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D9" s="4" t="n">
         <v>5688</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E9" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>모공주사 슈젝홈</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>댓글 · 링크</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>액티베이터 앰플을 먼저 왼쪽 먼저 진행을 할게요 가로 가로 2cm 세로 2cm 를 기본으로 들어가시고 앰플을 도포해 주시고 고정세로 그대로 가로 2cm 세로 2cm 그리고 가로 2cm 세로 2cm 이런 식으로 진행해 주시면 돼요 꾹 누르실 필요 없어요 살짝 피부에 닿았으면 닿았으면 살짝 눌러준다 정도로 진행을 하시고 무조건 흉터 있다고 해서 세게 하는 거 절대 좋지 않아요</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>모공주사 슈젝홈
 모공축소로 유명해진 슈젝홈
@@ -1169,51 +1008,51 @@
 22일 최저가링크는 댓글 🔻모공🔻달아주시면 안내해드릴게요</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="6" t="n">
+    <row r="10" ht="90" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>2026-07-15 23:51</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="D10" s="8" t="n">
         <v>3579</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E10" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>22일에 20% 추가할인</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>댓글 · 할인</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>여러분 7월 22일에 역대 최대 할인 20% 추가 할인을 진행을 해요 역대 최대 할인이어서 다들 쟁이시려고 대기하고 계세요 이건 무조건 조기품들이에요 제가 가장 빠르게 안내해드리는 대기방 만들어놨는데 안전하게 최대 할인가로 구매하실 분들은 댓글에 모공 달아주세요</t>
         </is>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>22일에 20% 추가할인
 정가 40만원대
@@ -1223,223 +1062,51 @@
 궁금하신분들은 댓글 모공 달아주세요</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 23:43</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-14 23:55</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>릴스</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>23498</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>얼리썸머 두번째 프로모션</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>링크 · 프로필 · 디엠 · 오픈</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>얼리썸머 두번째 프로모션
-내일 오후 한시 오픈됩니다!
-즉시구매는 프로필링크+스토리
-상담은 디엠주세요🙌🏻</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-15 23:41</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>에스테틱 시장은</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>오픈</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>에스테틱 시장은
-슈퍼젝션을 하는샵 VS 그렇지 않은 샵으로 나뉩니다.
-하고안하고의 고민이 아닌
-어떻게 할것이냐의 고민으로 넘어온 이때
-그동안 궁금했던 슈퍼젝션에 관한 모든것
-전국 최대기관 슈컬트에서 주관하는
-프리뷰 클래스에서 오픈합니다.
-무조건적인 바이럴이 아닌
-실제 고객님 피부상태에 따른 적용법부터
-내 샵의 컨셉에 맞는 상담+동선까지.
-궁금해하시던 모든내용들 프리뷰클래스에서 오픈됩니다.
-#슈퍼젝션 #슈젝</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 11:53</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>오늘 자정마감되는 메가실리엄</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>마감</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>오늘 자정마감되는 메가실리엄
-턱드름,입주변트러블,귀주변염증 등
-반복되는 문제성피부는 반드시 장의 이슈를 동반합니다.
-하루 한번으로
-유산균부터 비타민 B,D,E 비오틴 식이섬유까지 
-📍부작용은 변비대탈출📍</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14 23:55</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>릴스</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>23498</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>모공주사 원데이 D-7</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>대기방 · 신청</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>스타터 앰플이 있거든요 이 앰플을 어떻게 따라 하는지 물어보시는 분들이 많은데 그냥 옆으로 이렇게 미시면 돼요 미면 툭지에 연결을 해서 바로 얼굴에 즉시 도포 해주시는 거예요 애들은 약간 꾸덕해요 앰플이 그래서 충분히 내려올게끔 기다려주시고 이 상태로 얼굴에 도포 그리고 얼굴에 도포 해주시는 거예요 이렇게 도포해 주시면 한 병을 다 흡수시켜 주시는 거예요</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>모공주사 원데이 D-7
 그냥 구매하시는 분들을 위한 상세 사용법 올려드리는중...🙌🏻
@@ -1448,51 +1115,51 @@
 #모공주사 #슈젝홈</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="90" customHeight="1">
-      <c r="A18" s="2" t="n">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>2026-07-14 23:41</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D12" s="10" t="n">
         <v>11931</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>모공주사 구성은 이렇습니다🙌🏻</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>대기방 · 링크 · 할인</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>그래서 앰플은 열어보시면 액티브 크림 하나랑 앰플이 총 8병이 들어있어요 스타터 액티베이터 이렇게 들어있어요 그래서 이 스타터랑 액티베이터를 한 번에 같이 쓰시는 거예요 그래서 총 4회분이 들어있는 거죠 이들은 이렇게 되어 있어요 제가 수작을 지금 하는 걸 보여드릴 건데 이들은 이렇게 되어 있고 이들은 한 번 사용하시면 무조건 폐기 처분 버리셔야 돼요 재사용 안 돼요</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>모공주사 구성은 이렇습니다🙌🏻
 📌원데이 프로모션 이제 일주일 남았어요.
@@ -1501,217 +1168,51 @@
 대기방 링크는 스토리 띄워둘게요🙌🏻</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="90" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-14 19:12</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+    <row r="13" ht="90" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:52</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>릴스</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>10085</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>모공주사의 구성이 변경됩니다.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Vip 쿠폰 10분 한정 선착순 진행</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>선착순</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>Vip 쿠폰 10분 한정 선착순 진행
-회원분들만 가능합니다!
-반짝 진행이고 선착순으로 진행됩니다 ㅎㅎ</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
-      <c r="A20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-13 22:55</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>슈젝홈은 뛰어난 제품인만큼</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>신청</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>슈젝홈은 뛰어난 제품인만큼
-사용법에 따라 정말 큰 성능차이를 보여요.
-제대로 효과를 못봤다면 무조건 코칭신청
-그냥 구매하시는 분들이 많아 사용법도 피드에
-고정해뒀어요!
-어려운분들은 무조건 코칭신청🔥</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>2026-07-13 22:44</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>서포터 변경방법 안내🙌🏻</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>디엠 · 문의</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>서포터 변경방법 안내🙌🏻
-매일 들어오는 문의중
-정말 안타까운 문의들은 구매 후 제대로된 코칭을
-못받은 상황들인거같아요.
-간단하게 서포터 변경 후 코치가능합니다.
-코칭을 원하시는 분들은 디엠남겨주세요.
-#슈젝홈</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-13 21:52</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>릴스</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>10085</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>모공주사의 구성이 변경됩니다.</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>슈퍼젝션을 시키시면 이제 구성이 바뀌었어요 기존에 나가던 니들이 품절에 따라서 전문가용 니들로 교체가 돼서 나가요 그래서 앰플 하나를 주문을 하시면 기본적으로 어플리케이터가 두 개가 따르나가요 이 어플리케이터는 멸균 니들로 멸균 포장이 되어 있어요 그래서 이렇게 들어 있거든요 그래서 전문가용 니들이 총 두 개 두 개랑 앰플 4회분이 같이 발송이 돼요 그래서 여러분들이 추가로 구매하실 건 니들을 두 개를 추가를 하셔야 돼요 한번 쓰고 폐기 처분해야 하기 때문에 니들을 총 네 개가 필요해요 그래서 기본으로 두 개가 딸려 가니까 두 개만 추가해서 구매하시면 돼요</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>모공주사의 구성이 변경됩니다.
 (기존니들 품절로 전문가용 발송)
@@ -1721,51 +1222,51 @@
 2개만 추가해서 구매하시면 됩니다!</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="90" customHeight="1">
-      <c r="A23" s="6" t="n">
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>2026-07-13 19:39</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n">
+      <c r="D14" s="8" t="n">
         <v>3982</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>모공주사 대기방 입장링크 보내드립니다🙌🏻</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 링크 · 할인</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>여러분 홈키트 지금 이제 디데이 9일이에요. 9일 뒤에 20% 추가 할인 할 거고 미리 준비를 해두셔야 돼요. 단독방에 입장하시고 회원가입 미리 해두시고 주소까지 입력을 해주셔야지 품절 없이 무난하게 구매 가능하실 거예요. 댓글 달아주시면 대기방 링크 보내드릴게요.</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>모공주사 대기방 입장링크 보내드립니다🙌🏻
 이도저도 안되는 모공 포기하지말고
@@ -1779,51 +1280,51 @@
 구매 원하시는 분들은 댓글 🔻대기🔻남겨주세요🙌🏻</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="2" t="n">
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>2026-07-13 00:10</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D15" s="10" t="n">
         <v>18443</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">시간이 지날수록 자꾸 늘어지는 모공 </t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>할인</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>시간이 지날수록 자꾸 늘어지는 모공 
 줄이려면 상처를 내고 이걸 재생하는 과정을 거쳐야해요. 
@@ -1838,51 +1339,51 @@
 궁금하신분들 계실까요?</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="90" customHeight="1">
-      <c r="A25" s="6" t="n">
+    <row r="16" ht="90" customHeight="1">
+      <c r="A16" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>2026-07-12 21:37</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D25" s="8" t="n">
+      <c r="D16" s="8" t="n">
         <v>7772</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E16" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="F16" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>모공에 심는 모공주사</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>할인</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>모공에 심는 모공주사
 일주일에 한번 5만원대로 가능한 모공주사
@@ -1890,51 +1391,51 @@
 #모공주사 #슈젝홈</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="90" customHeight="1">
-      <c r="A26" s="2" t="n">
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>2026-07-12 18:33</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <v>90925</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>332</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>10년 넘게 모공에 미쳐본 결과</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 할인</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>10년 넘게 모공에 미쳐본 결과
 모공주사만한게 없어요.
@@ -1949,51 +1450,51 @@
 궁금하신분들은 댓글 달아주시면 대기방 안내해드릴게요!</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="6" t="n">
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>2026-07-11 01:46</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D27" s="8" t="n">
+      <c r="D18" s="8" t="n">
         <v>6521</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="E18" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">🙆🏻‍♂️모공주사는 모공을 완전히 없어지게 만드는 시술이 아닙니다. </t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 할인</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>🙆🏻‍♂️모공주사는 모공을 완전히 없어지게 만드는 시술이 아닙니다. 
 모공을 완전히 없앨 수도 없구요. 
@@ -2012,51 +1513,51 @@
 댓글 🔻모공🔻 달아주시면 즉시구매부터 대기방까지 안내해드립니다.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="A28" s="2" t="n">
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>2026-07-11 00:38</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D19" s="4" t="n">
         <v>5049</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>마지막 보시면 아시겠지만,</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>마지막 보시면 아시겠지만,
 문제는 이름이 아니었음.
@@ -2065,51 +1566,51 @@
 무튼 청춘미남은 이렇게 탄생했습니다🙆🏻‍♂️</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="90" customHeight="1">
-      <c r="A29" s="6" t="n">
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>2026-07-10 22:23</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>릴스</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D20" s="11" t="n">
         <v>11988</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E20" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F20" s="8" t="n">
         <v>237</v>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>프로모션만 열리면 대란인 슈젝홈</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>댓글 · 대기방 · 링크 · 할인</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>(전사없음)</t>
         </is>
       </c>
-      <c r="J29" s="7" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>프로모션만 열리면 대란인 슈젝홈
 7월 22일 역대 최대 할인인 20% 추가할인을 진행합니다.
@@ -2120,160 +1621,45 @@
 입장원하시는 분들은 댓글 🔻모공🔻 남겨주세요.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>열기 ↗</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="90" customHeight="1">
-      <c r="A30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-10 19:20</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>신상오픈 폴리싱A,스타터A</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>디엠 · 문의 · 오픈</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>신상오픈 폴리싱A,스타터A
-기존의 딥클렌징,
-자극적인 각질제거가 아닌
-📍곤약스크럽이 피부각질제거,트러블발생 억제까지
-트러블 피부라면 지금부터 곤약스크럽+아크네스타터
-트러블로 인한 피부에 맞춰 딥클렌징+트러블 감소+예방까지
-해줘요
-구매문의는 디엠📩</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="90" customHeight="1">
-      <c r="A31" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-11 16:40</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>캐러셀</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>문의가 밀린 관계로</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>DM · 문의</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>(캐러셀·전사없음)</t>
-        </is>
-      </c>
-      <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>문의가 밀린 관계로
-미리 올려드리는 슈젝홈 사용법✨
-사용법이 헷갈리시는 분들 참고용
-📌구매 후 꼭 피부타입별 코칭받고 사용하세요.
-구매 후 DM📩 
-순차적으로 피부진단+사용법까지 안내해드립니다.
-#슈퍼젝션 #슈퍼젝션홈키트</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>열기 ↗</t>
-        </is>
-      </c>
-    </row>
+    <row r="21" ht="90" customHeight="1"/>
+    <row r="22" ht="90" customHeight="1"/>
+    <row r="23" ht="90" customHeight="1"/>
+    <row r="24" ht="90" customHeight="1"/>
+    <row r="25" ht="90" customHeight="1"/>
+    <row r="26" ht="90" customHeight="1"/>
+    <row r="27" ht="90" customHeight="1"/>
+    <row r="28" ht="90" customHeight="1"/>
+    <row r="29" ht="90" customHeight="1"/>
+    <row r="30" ht="90" customHeight="1"/>
+    <row r="31" ht="90" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:K31"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2285,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2308,13 +1694,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>총 게시물</t>
+          <t>분석 릴스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>릴스</t>
@@ -2323,14 +1708,15 @@
       <c r="E3" t="n">
         <v>19</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>캐러셀</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>11</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>정성분석(§05)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2342,7 +1728,6 @@
       <c r="B4" t="n">
         <v>13281</v>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>최고 조회</t>
@@ -2351,7 +1736,6 @@
       <c r="E4" t="n">
         <v>90925</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>최저</t>
@@ -2547,6 +1931,20 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>모공에 심는 모공주사</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>※ 캐러셀 11개는 인스타가 조회수를 주지 않는 포맷 → 수치표에서 제외.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   커버 템플릿·포지셔닝 등 구조 분석은 리포트 §05(벤치마크) 참고.</t>
         </is>
       </c>
     </row>
